--- a/GameConfig/Datas/skill_level.xlsx
+++ b/GameConfig/Datas/skill_level.xlsx
@@ -639,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -988,6 +988,566 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B17" s="17">
+        <v>150002</v>
+      </c>
+      <c r="C17" s="18">
+        <v>1500</v>
+      </c>
+      <c r="D17" s="18">
+        <v>2</v>
+      </c>
+      <c r="E17" s="18">
+        <v>0</v>
+      </c>
+      <c r="F17" s="19">
+        <v>0</v>
+      </c>
+      <c r="G17" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B18" s="14">
+        <v>150003</v>
+      </c>
+      <c r="C18" s="15">
+        <v>1500</v>
+      </c>
+      <c r="D18" s="15">
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
+      </c>
+      <c r="F18" s="16">
+        <v>0</v>
+      </c>
+      <c r="G18" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B19" s="17">
+        <v>150004</v>
+      </c>
+      <c r="C19" s="18">
+        <v>1500</v>
+      </c>
+      <c r="D19" s="18">
+        <v>4</v>
+      </c>
+      <c r="E19" s="18">
+        <v>0</v>
+      </c>
+      <c r="F19" s="19">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B20" s="14">
+        <v>150005</v>
+      </c>
+      <c r="C20" s="15">
+        <v>1500</v>
+      </c>
+      <c r="D20" s="15">
+        <v>5</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
+      </c>
+      <c r="F20" s="16">
+        <v>0</v>
+      </c>
+      <c r="G20" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B21" s="17">
+        <v>150102</v>
+      </c>
+      <c r="C21" s="18">
+        <v>1501</v>
+      </c>
+      <c r="D21" s="18">
+        <v>2</v>
+      </c>
+      <c r="E21" s="18">
+        <v>0</v>
+      </c>
+      <c r="F21" s="19">
+        <v>0</v>
+      </c>
+      <c r="G21" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B22" s="14">
+        <v>150103</v>
+      </c>
+      <c r="C22" s="15">
+        <v>1501</v>
+      </c>
+      <c r="D22" s="15">
+        <v>3</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
+      </c>
+      <c r="F22" s="16">
+        <v>0</v>
+      </c>
+      <c r="G22" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B23" s="17">
+        <v>150104</v>
+      </c>
+      <c r="C23" s="18">
+        <v>1501</v>
+      </c>
+      <c r="D23" s="18">
+        <v>4</v>
+      </c>
+      <c r="E23" s="18">
+        <v>0</v>
+      </c>
+      <c r="F23" s="19">
+        <v>0</v>
+      </c>
+      <c r="G23" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B24" s="14">
+        <v>150105</v>
+      </c>
+      <c r="C24" s="15">
+        <v>1501</v>
+      </c>
+      <c r="D24" s="15">
+        <v>5</v>
+      </c>
+      <c r="E24" s="15">
+        <v>0</v>
+      </c>
+      <c r="F24" s="16">
+        <v>0</v>
+      </c>
+      <c r="G24" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B25" s="17">
+        <v>150202</v>
+      </c>
+      <c r="C25" s="18">
+        <v>1502</v>
+      </c>
+      <c r="D25" s="18">
+        <v>2</v>
+      </c>
+      <c r="E25" s="18">
+        <v>0</v>
+      </c>
+      <c r="F25" s="19">
+        <v>0</v>
+      </c>
+      <c r="G25" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B26" s="14">
+        <v>150203</v>
+      </c>
+      <c r="C26" s="15">
+        <v>1502</v>
+      </c>
+      <c r="D26" s="15">
+        <v>3</v>
+      </c>
+      <c r="E26" s="15">
+        <v>0</v>
+      </c>
+      <c r="F26" s="16">
+        <v>0</v>
+      </c>
+      <c r="G26" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B27" s="17">
+        <v>150204</v>
+      </c>
+      <c r="C27" s="18">
+        <v>1502</v>
+      </c>
+      <c r="D27" s="18">
+        <v>4</v>
+      </c>
+      <c r="E27" s="18">
+        <v>0</v>
+      </c>
+      <c r="F27" s="19">
+        <v>0</v>
+      </c>
+      <c r="G27" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B28" s="14">
+        <v>150205</v>
+      </c>
+      <c r="C28" s="15">
+        <v>1502</v>
+      </c>
+      <c r="D28" s="15">
+        <v>5</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
+      </c>
+      <c r="F28" s="16">
+        <v>0</v>
+      </c>
+      <c r="G28" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B29" s="17">
+        <v>150302</v>
+      </c>
+      <c r="C29" s="18">
+        <v>1503</v>
+      </c>
+      <c r="D29" s="18">
+        <v>2</v>
+      </c>
+      <c r="E29" s="18">
+        <v>0</v>
+      </c>
+      <c r="F29" s="19">
+        <v>0</v>
+      </c>
+      <c r="G29" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B30" s="14">
+        <v>150303</v>
+      </c>
+      <c r="C30" s="15">
+        <v>1503</v>
+      </c>
+      <c r="D30" s="15">
+        <v>3</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
+      </c>
+      <c r="F30" s="16">
+        <v>0</v>
+      </c>
+      <c r="G30" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B31" s="17">
+        <v>150304</v>
+      </c>
+      <c r="C31" s="18">
+        <v>1503</v>
+      </c>
+      <c r="D31" s="18">
+        <v>4</v>
+      </c>
+      <c r="E31" s="18">
+        <v>0</v>
+      </c>
+      <c r="F31" s="19">
+        <v>0</v>
+      </c>
+      <c r="G31" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B32" s="14">
+        <v>150305</v>
+      </c>
+      <c r="C32" s="15">
+        <v>1503</v>
+      </c>
+      <c r="D32" s="15">
+        <v>5</v>
+      </c>
+      <c r="E32" s="15">
+        <v>0</v>
+      </c>
+      <c r="F32" s="16">
+        <v>0</v>
+      </c>
+      <c r="G32" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B33" s="17">
+        <v>150402</v>
+      </c>
+      <c r="C33" s="18">
+        <v>1504</v>
+      </c>
+      <c r="D33" s="18">
+        <v>2</v>
+      </c>
+      <c r="E33" s="18">
+        <v>0</v>
+      </c>
+      <c r="F33" s="19">
+        <v>0</v>
+      </c>
+      <c r="G33" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B34" s="14">
+        <v>150403</v>
+      </c>
+      <c r="C34" s="15">
+        <v>1504</v>
+      </c>
+      <c r="D34" s="15">
+        <v>3</v>
+      </c>
+      <c r="E34" s="15">
+        <v>0</v>
+      </c>
+      <c r="F34" s="16">
+        <v>0</v>
+      </c>
+      <c r="G34" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B35" s="17">
+        <v>150404</v>
+      </c>
+      <c r="C35" s="18">
+        <v>1504</v>
+      </c>
+      <c r="D35" s="18">
+        <v>4</v>
+      </c>
+      <c r="E35" s="18">
+        <v>0</v>
+      </c>
+      <c r="F35" s="19">
+        <v>0</v>
+      </c>
+      <c r="G35" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B36" s="14">
+        <v>150405</v>
+      </c>
+      <c r="C36" s="15">
+        <v>1504</v>
+      </c>
+      <c r="D36" s="15">
+        <v>5</v>
+      </c>
+      <c r="E36" s="15">
+        <v>0</v>
+      </c>
+      <c r="F36" s="16">
+        <v>0</v>
+      </c>
+      <c r="G36" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B37" s="17">
+        <v>150602</v>
+      </c>
+      <c r="C37" s="18">
+        <v>1506</v>
+      </c>
+      <c r="D37" s="18">
+        <v>2</v>
+      </c>
+      <c r="E37" s="18">
+        <v>0</v>
+      </c>
+      <c r="F37" s="19">
+        <v>0</v>
+      </c>
+      <c r="G37" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B38" s="14">
+        <v>150603</v>
+      </c>
+      <c r="C38" s="15">
+        <v>1506</v>
+      </c>
+      <c r="D38" s="15">
+        <v>3</v>
+      </c>
+      <c r="E38" s="15">
+        <v>0</v>
+      </c>
+      <c r="F38" s="16">
+        <v>0</v>
+      </c>
+      <c r="G38" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B39" s="17">
+        <v>150604</v>
+      </c>
+      <c r="C39" s="18">
+        <v>1506</v>
+      </c>
+      <c r="D39" s="18">
+        <v>4</v>
+      </c>
+      <c r="E39" s="18">
+        <v>0</v>
+      </c>
+      <c r="F39" s="19">
+        <v>0</v>
+      </c>
+      <c r="G39" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B40" s="14">
+        <v>150605</v>
+      </c>
+      <c r="C40" s="15">
+        <v>1506</v>
+      </c>
+      <c r="D40" s="15">
+        <v>5</v>
+      </c>
+      <c r="E40" s="15">
+        <v>0</v>
+      </c>
+      <c r="F40" s="16">
+        <v>0</v>
+      </c>
+      <c r="G40" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B41" s="17">
+        <v>150702</v>
+      </c>
+      <c r="C41" s="18">
+        <v>1507</v>
+      </c>
+      <c r="D41" s="18">
+        <v>2</v>
+      </c>
+      <c r="E41" s="18">
+        <v>0</v>
+      </c>
+      <c r="F41" s="19">
+        <v>0</v>
+      </c>
+      <c r="G41" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B42" s="14">
+        <v>150703</v>
+      </c>
+      <c r="C42" s="15">
+        <v>1507</v>
+      </c>
+      <c r="D42" s="15">
+        <v>3</v>
+      </c>
+      <c r="E42" s="15">
+        <v>0</v>
+      </c>
+      <c r="F42" s="16">
+        <v>0</v>
+      </c>
+      <c r="G42" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B43" s="17">
+        <v>150704</v>
+      </c>
+      <c r="C43" s="18">
+        <v>1507</v>
+      </c>
+      <c r="D43" s="18">
+        <v>4</v>
+      </c>
+      <c r="E43" s="18">
+        <v>0</v>
+      </c>
+      <c r="F43" s="19">
+        <v>0</v>
+      </c>
+      <c r="G43" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="22.5" customHeight="1">
+      <c r="B44" s="14">
+        <v>150705</v>
+      </c>
+      <c r="C44" s="15">
+        <v>1507</v>
+      </c>
+      <c r="D44" s="15">
+        <v>5</v>
+      </c>
+      <c r="E44" s="15">
+        <v>0</v>
+      </c>
+      <c r="F44" s="16">
+        <v>0</v>
+      </c>
+      <c r="G44" s="16">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
